--- a/sheets/민요/검수/선화공주.xlsx
+++ b/sheets/민요/검수/선화공주.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +131,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3161,8 +3220,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3177,720 +3240,611 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선화공주 — 민요채보-1/선화공주.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">선화공주</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 汰</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" s="12"/>
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 汰</t>
         </is>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="12"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="12"/>
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" s="12"/>
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 湳</t>
         </is>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="K3" s="13"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="13"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="13"/>
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="13"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 湳</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="13"/>
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" s="13"/>
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="K4" s="13"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="13"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 湳</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="13"/>
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="13"/>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="13"/>
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" s="13"/>
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="L5" s="10"/>
+      <c r="M5" s="13"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="13"/>
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="13"/>
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="13"/>
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="13"/>
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="K6" s="13"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="13"/>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="13"/>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="12"/>
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="13"/>
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="L7" s="10"/>
+      <c r="M7" s="13"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="13"/>
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="13"/>
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="13"/>
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="13"/>
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="K8" s="13"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="13"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="12"/>
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="13"/>
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="13"/>
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="13"/>
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="L9" s="10"/>
+      <c r="M9" s="13"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 △</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="13"/>
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="13"/>
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 姑</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="13"/>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="I10" s="13"/>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="K10" s="12"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="13"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" s="13"/>
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="12"/>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 湳</t>
         </is>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="G11" s="12"/>
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">西
 姑</t>
         </is>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="14"/>
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 湳</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="L11" s="10"/>
+      <c r="M11" s="13"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="12"/>
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="13"/>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 姑</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="13"/>
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="13"/>
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K12" s="13"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="13"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="10"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="13"/>
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" s="13"/>
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" s="13"/>
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K13" s="13"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="10"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 黃</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="13"/>
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="13"/>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="13"/>
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K14" s="13"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="13"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="10"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 湳</t>
         </is>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" s="13"/>
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G15" s="13"/>
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 黃</t>
         </is>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I15" s="13"/>
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K15" s="13"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="10"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="13"/>
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" s="13"/>
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I16" s="13"/>
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K16" s="13"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="13"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="10"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E17" s="13"/>
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G17" s="12"/>
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="I17" s="13"/>
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K17" s="13"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="10"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E18" s="13"/>
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="G18" s="12"/>
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="I18" s="12"/>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K18" s="3"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/선화공주.xlsx
+++ b/sheets/민요/검수/선화공주.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -549,13 +549,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―</t>
+          <t xml:space="preserve">㴌|–</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―</t>
+–</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -628,13 +628,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―汰</t>
+          <t xml:space="preserve">㴌|–汰</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -786,13 +786,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -861,13 +861,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳|―</t>
+          <t xml:space="preserve">湳|–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1098,13 +1098,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1331,13 +1331,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1486,13 +1486,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1723,13 +1723,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1798,13 +1798,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―㴌</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -1952,13 +1952,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無|―㴌</t>
+          <t xml:space="preserve">潢無|–㴌</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2107,13 +2107,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―淋</t>
+          <t xml:space="preserve">㴌|–淋</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―淋</t>
+–淋</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2186,13 +2186,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋|―</t>
+          <t xml:space="preserve">淋|–</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I45" s="2"/>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I46" s="2"/>
@@ -2331,13 +2331,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2402,13 +2402,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―</t>
+          <t xml:space="preserve">㴌|–</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―</t>
+–</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2481,13 +2481,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳|―</t>
+          <t xml:space="preserve">湳|–</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―</t>
+–</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2560,13 +2560,13 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―㴌</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2755,12 +2755,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -2790,13 +2790,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I60" s="2"/>
@@ -2901,13 +2901,13 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2980,13 +2980,13 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳|―</t>
+          <t xml:space="preserve">湳|–</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―</t>
+–</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3221,13 +3221,13 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I73" s="2"/>
@@ -3393,7 +3393,7 @@
       <c r="B3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―</t>
+–</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -3404,7 +3404,7 @@
       <c r="D3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―</t>
+–</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -3415,7 +3415,7 @@
       <c r="F3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -3437,7 +3437,7 @@
       <c r="J3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―</t>
+–</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       <c r="D5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―</t>
+–</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -3552,7 +3552,7 @@
       <c r="J5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G6" s="10"/>
@@ -3626,7 +3626,7 @@
       <c r="D7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -3637,7 +3637,7 @@
       <c r="F7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -3648,7 +3648,7 @@
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -3730,7 +3730,7 @@
       <c r="B9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -3774,7 +3774,7 @@
       <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
@@ -3795,21 +3795,21 @@
       <c r="C10" s="10"/>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3827,7 +3827,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C11" s="8"/>
@@ -3845,7 +3845,7 @@
       <c r="F11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―淋</t>
+–淋</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -3856,7 +3856,7 @@
       <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -3867,7 +3867,7 @@
       <c r="J11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―</t>
+–</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -3888,7 +3888,7 @@
       <c r="C12" s="9"/>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E12" s="9"/>
@@ -3931,15 +3931,15 @@
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -3984,7 +3984,7 @@
       <c r="E14" s="10"/>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="10"/>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G15" s="8"/>
@@ -4099,7 +4099,7 @@
       <c r="D17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -4109,15 +4109,15 @@
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -4128,7 +4128,7 @@
       <c r="J17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">

--- a/sheets/민요/검수/선화공주.xlsx
+++ b/sheets/민요/검수/선화공주.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3371,808 +3406,808 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">선화공주</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 –</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –㴌</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼굴</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">부키</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">선</t>
         </is>
       </c>
-      <c r="L3" s="17"/>
-      <c r="M3" s="8"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L4" s="17"/>
-      <c r="M4" s="9"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢㴌
 潢無</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">왕자</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 –</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화끈</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">명화</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –汰</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">공주</t>
         </is>
       </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="9"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="25"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="26"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="26"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="L6" s="17"/>
-      <c r="M6" s="10"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="26"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
 南</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">찜했다</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –㴌</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">첫</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
 –㴌</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가슴</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無㴌
 潢無</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">바보</t>
         </is>
       </c>
-      <c r="L7" s="17"/>
-      <c r="M7" s="8"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="L8" s="17"/>
-      <c r="M8" s="9"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑을</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">두근</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리고</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L9" s="17"/>
-      <c r="M9" s="9"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="25"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="26"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="26"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="26"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="10"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">스리</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –淋</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">서동</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 –</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">선</t>
         </is>
       </c>
-      <c r="L11" s="17"/>
-      <c r="M11" s="8"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="22"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="25"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="25"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">왕</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">직</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L12" s="17"/>
-      <c r="M12" s="9"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="25"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 –</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢㴌
 潢無</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢㴌
 潢無</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">공주</t>
         </is>
       </c>
-      <c r="L13" s="17"/>
-      <c r="M13" s="9"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="26"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="L14" s="17"/>
-      <c r="M14" s="10"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="26"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">스리</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="G15" s="22"/>
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
 南</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">하나</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
 南</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">바보</t>
         </is>
       </c>
-      <c r="L15" s="17"/>
-      <c r="M15" s="8"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="22"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="B16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="25"/>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="L16" s="17"/>
-      <c r="M16" s="9"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="B17" s="21"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">살</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="G17" s="25"/>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L17" s="17"/>
-      <c r="M17" s="9"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="25"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="B18" s="21"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">짝</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="26"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="I18" s="26"/>
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="10"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/선화공주.xlsx
+++ b/sheets/민요/검수/선화공주.xlsx
@@ -3387,24 +3387,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
       <c r="L3" s="21"/>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
       <c r="L4" s="21"/>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
       <c r="L5" s="21"/>
       <c r="M5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
       <c r="G6" s="26"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="26"/>
@@ -3645,7 +3645,7 @@
       <c r="L6" s="21"/>
       <c r="M6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       <c r="L7" s="21"/>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
       <c r="L8" s="21"/>
       <c r="M8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       <c r="L9" s="21"/>
       <c r="M9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
       <c r="L10" s="21"/>
       <c r="M10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
       <c r="L11" s="21"/>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
       <c r="L12" s="21"/>
       <c r="M12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -4007,7 +4007,7 @@
       <c r="L13" s="21"/>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -4046,7 +4046,7 @@
       <c r="L14" s="21"/>
       <c r="M14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4092,7 +4092,7 @@
       <c r="L15" s="21"/>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -4100,7 +4100,7 @@
       <c r="E16" s="25"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G16" s="25"/>
@@ -4127,7 +4127,7 @@
       <c r="L16" s="21"/>
       <c r="M16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -4174,7 +4174,7 @@
       <c r="L17" s="21"/>
       <c r="M17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>

--- a/sheets/민요/검수/선화공주.xlsx
+++ b/sheets/민요/검수/선화공주.xlsx
@@ -3455,7 +3455,8 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">얼굴</t>
+          <t xml:space="preserve">얼
+굴</t>
         </is>
       </c>
       <c r="H3" s="23" t="inlineStr">
@@ -3466,7 +3467,8 @@
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">부키</t>
+          <t xml:space="preserve">부
+키</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
@@ -3548,7 +3550,8 @@
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">왕자</t>
+          <t xml:space="preserve">왕
+자</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -3570,7 +3573,8 @@
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">화끈</t>
+          <t xml:space="preserve">화
+끈</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -3581,7 +3585,8 @@
       </c>
       <c r="I5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">명화</t>
+          <t xml:space="preserve">명
+화</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -3592,7 +3597,8 @@
       </c>
       <c r="K5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">공주</t>
+          <t xml:space="preserve">공
+주</t>
         </is>
       </c>
       <c r="L5" s="21"/>
@@ -3655,7 +3661,9 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">찜했다</t>
+          <t xml:space="preserve">찜
+했
+다</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -3677,7 +3685,8 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">가슴</t>
+          <t xml:space="preserve">가
+슴</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -3699,7 +3708,8 @@
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">바보</t>
+          <t xml:space="preserve">바
+보</t>
         </is>
       </c>
       <c r="L7" s="21"/>
@@ -3781,7 +3791,8 @@
       </c>
       <c r="E9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑을</t>
+          <t xml:space="preserve">랑
+을</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -3792,7 +3803,8 @@
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">두근</t>
+          <t xml:space="preserve">두
+근</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -3803,7 +3815,8 @@
       </c>
       <c r="I9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">리고</t>
+          <t xml:space="preserve">리
+고</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -3874,7 +3887,8 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">스리</t>
+          <t xml:space="preserve">스
+리</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -3885,7 +3899,8 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">서동</t>
+          <t xml:space="preserve">서
+동</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -4001,7 +4016,8 @@
       </c>
       <c r="K13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">공주</t>
+          <t xml:space="preserve">공
+주</t>
         </is>
       </c>
       <c r="L13" s="21"/>
@@ -4058,7 +4074,8 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">스리</t>
+          <t xml:space="preserve">스
+리</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -4075,7 +4092,8 @@
       </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나</t>
+          <t xml:space="preserve">하
+나</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -4086,7 +4104,8 @@
       </c>
       <c r="K15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">바보</t>
+          <t xml:space="preserve">바
+보</t>
         </is>
       </c>
       <c r="L15" s="21"/>

--- a/sheets/민요/검수/선화공주.xlsx
+++ b/sheets/민요/검수/선화공주.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -230,6 +235,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3431,7 +3448,7 @@
 –</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -3442,7 +3459,7 @@
 –</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -3453,7 +3470,7 @@
 –㴌</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">얼
 굴</t>
@@ -3465,7 +3482,7 @@
 南</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">부
 키</t>
@@ -3477,13 +3494,13 @@
 –</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">선</t>
         </is>
       </c>
       <c r="L3" s="21"/>
-      <c r="M3" s="22"/>
+      <c r="M3" s="27"/>
     </row>
     <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
@@ -3492,7 +3509,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -3502,7 +3519,7 @@
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -3512,7 +3529,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -3522,7 +3539,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
@@ -3532,13 +3549,13 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
       <c r="L4" s="21"/>
-      <c r="M4" s="25"/>
+      <c r="M4" s="29"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -3548,7 +3565,7 @@
 潢無</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">왕
 자</t>
@@ -3560,7 +3577,7 @@
 –</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -3571,7 +3588,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">화
 끈</t>
@@ -3583,7 +3600,7 @@
 南</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">명
 화</t>
@@ -3595,14 +3612,14 @@
 –汰</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">공
 주</t>
         </is>
       </c>
       <c r="L5" s="21"/>
-      <c r="M5" s="25"/>
+      <c r="M5" s="29"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -3611,7 +3628,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -3621,7 +3638,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -3631,25 +3648,25 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="30"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="26"/>
+      <c r="I6" s="30"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="K6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
       <c r="L6" s="21"/>
-      <c r="M6" s="26"/>
+      <c r="M6" s="30"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -3659,7 +3676,7 @@
 南</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">찜
 했
@@ -3672,7 +3689,7 @@
 –㴌</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">첫</t>
         </is>
@@ -3683,7 +3700,7 @@
 –㴌</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 슴</t>
@@ -3695,7 +3712,7 @@
 –</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -3706,14 +3723,14 @@
 潢無</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">바
 보</t>
         </is>
       </c>
       <c r="L7" s="21"/>
-      <c r="M7" s="22"/>
+      <c r="M7" s="27"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -3722,7 +3739,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -3732,7 +3749,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -3742,7 +3759,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -3752,7 +3769,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
@@ -3762,13 +3779,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K8" s="25" t="inlineStr">
+      <c r="K8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
       <c r="L8" s="21"/>
-      <c r="M8" s="25"/>
+      <c r="M8" s="29"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -3778,7 +3795,7 @@
 –</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -3789,7 +3806,7 @@
 姑</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">랑
 을</t>
@@ -3801,7 +3818,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">두
 근</t>
@@ -3813,7 +3830,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">리
 고</t>
@@ -3825,13 +3842,13 @@
 –</t>
         </is>
       </c>
-      <c r="K9" s="25" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
       <c r="L9" s="21"/>
-      <c r="M9" s="25"/>
+      <c r="M9" s="29"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
@@ -3840,36 +3857,36 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="30"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="30"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I10" s="26"/>
+      <c r="I10" s="30"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K10" s="26"/>
+      <c r="K10" s="30"/>
       <c r="L10" s="21"/>
-      <c r="M10" s="26"/>
+      <c r="M10" s="30"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -3878,14 +3895,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C11" s="22"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">스
 리</t>
@@ -3897,7 +3914,7 @@
 –淋</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">서
 동</t>
@@ -3909,7 +3926,7 @@
 –</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -3920,13 +3937,13 @@
 –</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">선</t>
         </is>
       </c>
       <c r="L11" s="21"/>
-      <c r="M11" s="22"/>
+      <c r="M11" s="27"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -3935,19 +3952,19 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C12" s="25"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="25"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">왕</t>
         </is>
@@ -3957,7 +3974,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">직</t>
         </is>
@@ -3967,32 +3984,32 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="25" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
       <c r="L12" s="21"/>
-      <c r="M12" s="25"/>
+      <c r="M12" s="29"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="25"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 –</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -4003,7 +4020,7 @@
 潢無</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -4014,37 +4031,37 @@
 潢無</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">공
 주</t>
         </is>
       </c>
       <c r="L13" s="21"/>
-      <c r="M13" s="25"/>
+      <c r="M13" s="29"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="26"/>
+      <c r="C14" s="30"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="30"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="30"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="I14" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -4054,25 +4071,25 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K14" s="26" t="inlineStr">
+      <c r="K14" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
       <c r="L14" s="21"/>
-      <c r="M14" s="26"/>
+      <c r="M14" s="30"/>
     </row>
     <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
-      <c r="C15" s="22"/>
+      <c r="C15" s="27"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">스
 리</t>
@@ -4083,14 +4100,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G15" s="22"/>
+      <c r="G15" s="27"/>
       <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
 南</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">하
 나</t>
@@ -4102,33 +4119,33 @@
 南</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">바
 보</t>
         </is>
       </c>
       <c r="L15" s="21"/>
-      <c r="M15" s="22"/>
+      <c r="M15" s="27"/>
     </row>
     <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
-      <c r="C16" s="25"/>
+      <c r="C16" s="29"/>
       <c r="D16" s="21"/>
-      <c r="E16" s="25"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G16" s="25"/>
+      <c r="G16" s="29"/>
       <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -4138,25 +4155,25 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K16" s="25" t="inlineStr">
+      <c r="K16" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
       <c r="L16" s="21"/>
-      <c r="M16" s="25"/>
+      <c r="M16" s="29"/>
     </row>
     <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
-      <c r="C17" s="25"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">살</t>
         </is>
@@ -4167,14 +4184,14 @@
 –</t>
         </is>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="29"/>
       <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -4185,24 +4202,24 @@
 –</t>
         </is>
       </c>
-      <c r="K17" s="25" t="inlineStr">
+      <c r="K17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
       <c r="L17" s="21"/>
-      <c r="M17" s="25"/>
+      <c r="M17" s="29"/>
     </row>
     <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
-      <c r="C18" s="26"/>
+      <c r="C18" s="30"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">짝</t>
         </is>
@@ -4212,21 +4229,21 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="26"/>
+      <c r="G18" s="30"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="26"/>
+      <c r="I18" s="30"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="26"/>
+      <c r="K18" s="30"/>
       <c r="L18" s="21"/>
-      <c r="M18" s="26"/>
+      <c r="M18" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/선화공주.xlsx
+++ b/sheets/민요/검수/선화공주.xlsx
@@ -399,7 +399,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독(이전 16정간·6줄 판독은 구조가 틀렸음). 16정간 양식(번호 1~16)이지만 굵은 선이 2칸마다이고 칸 안 가로선이 없어 큰 칸 8개, 칸마다 율명 2~4개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 줄 1 은 비어 인쇄 2~6줄을 줄1~5로, 7·8줄 비어 #줄수 5. 우측 여백 "(정악?)" "선화공주" "굿거리". 끝의 쉼표는 D·▷처럼 흘려 쓴 것도 △. 하단 "196" 무시. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독(이전 16정간·6줄 판독은 구조가 틀렸음). 16정간 양식(번호 1~16)이지만 굵은 선이 2칸마다이고 칸 안 가로선이 없어 큰 칸 8개, 칸마다 율명 2~4개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 줄 1 은 비어 인쇄 2~6줄을 줄1~5로, 7·8줄 비어 #줄수 5. 우측 여백 "(정악?)" "선화공주" "굿거리". 끝의 쉼표는 D·▷처럼 흘려 쓴 것도 △. 하단 "196" 무시. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 '부귀와'를 부키로 씀</t>
+          <t xml:space="preserve">가사 '부귀와'를 부키로 씀; 둘째·셋째 南/姑?</t>
         </is>
       </c>
       <c r="K10" s="2"/>

--- a/sheets/민요/검수/선화공주.xlsx
+++ b/sheets/민요/검수/선화공주.xlsx
@@ -675,10 +675,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/선화공주.xlsx
+++ b/sheets/민요/검수/선화공주.xlsx
@@ -565,25 +565,9 @@
 직</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌
+    <t xml:space="preserve">㴌
 㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+–</t>
   </si>
   <si>
     <t xml:space="preserve">–
@@ -616,17 +600,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -748,7 +732,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -802,6 +786,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2409,272 +2433,272 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:K10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="52.63" customHeight="true">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B3" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="18" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="21" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="9" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B5" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="21" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B6" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="23" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B7" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="18" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B8" s="17"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="21"/>
+      <c r="F8" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="21" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="9" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B9" s="17"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="7" t="s">
+      <c r="G9" s="21"/>
+      <c r="H9" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="21" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B10" s="17"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="23"/>
+      <c r="H10" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="23" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2684,7 +2708,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/선화공주.xlsx
+++ b/sheets/민요/검수/선화공주.xlsx
@@ -2439,15 +2439,15 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
   </cols>
   <sheetData>
